--- a/docs/downloads/04/tbl_origine_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_origine_alaotra_avaradrano.xlsx
@@ -512,12 +512,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>6.3</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
